--- a/7_weitere_beispiele/ue_2_bedingte_formatierung.xlsx
+++ b/7_weitere_beispiele/ue_2_bedingte_formatierung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a08e36333fa8bc9f/excel_20260302/7_weitere_beispiele/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a08e36333fa8bc9f/excel_20260302_ueberarbeitet/7_weitere_beispiele/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{9E9A0A12-ECB2-4033-AC99-95B0B941E2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBE3CD86-0858-4870-9016-F9EFF8928889}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{9E9A0A12-ECB2-4033-AC99-95B0B941E2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DBE73BD-3587-4794-BBDD-1158744B55BF}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2A5CF1C8-7A37-40AD-AEF9-57995A3284A3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A5CF1C8-7A37-40AD-AEF9-57995A3284A3}"/>
   </bookViews>
   <sheets>
     <sheet name="vkzahlen" sheetId="1" r:id="rId1"/>
@@ -86,9 +86,6 @@
     <t>Produkt 3</t>
   </si>
   <si>
-    <t>Es soll mit Ampelsysmbolen markiert werden, welche Produkte sich in welchen Monaten gut bzw. weniger gut verkauft haben.</t>
-  </si>
-  <si>
     <t>- rot: &lt; 5.000 Stück</t>
   </si>
   <si>
@@ -105,6 +102,9 @@
   </si>
   <si>
     <t>Mache eine Kopie der Tabelle und probiere auch die bedingte Formatierung "Datenbalken" aus.</t>
+  </si>
+  <si>
+    <t>Es soll mit Ampelsymbolen markiert werden, welche Produkte sich in welchen Monaten gut bzw. weniger gut verkauft haben.</t>
   </si>
 </sst>
 </file>
@@ -548,7 +548,7 @@
         <v>11285</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -565,7 +565,7 @@
         <v>8851</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -582,7 +582,7 @@
         <v>15811</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -599,7 +599,7 @@
         <v>16895</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -616,7 +616,7 @@
         <v>19891</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -661,7 +661,7 @@
         <v>3218</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -678,7 +678,7 @@
         <v>10463</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
